--- a/artfynd/A 7763-2026 artfynd.xlsx
+++ b/artfynd/A 7763-2026 artfynd.xlsx
@@ -1395,7 +1395,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131194260</v>
+        <v>131194264</v>
       </c>
       <c r="B8" t="n">
         <v>57884</v>
@@ -1438,10 +1438,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>599106</v>
+        <v>599123</v>
       </c>
       <c r="R8" t="n">
-        <v>6943538</v>
+        <v>6943474</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1473,7 +1473,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>färska ringhack på tall</t>
+          <t>färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1515,7 +1515,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131194264</v>
+        <v>131194260</v>
       </c>
       <c r="B9" t="n">
         <v>57884</v>
@@ -1558,10 +1558,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>599123</v>
+        <v>599106</v>
       </c>
       <c r="R9" t="n">
-        <v>6943474</v>
+        <v>6943538</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1593,7 +1593,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1603,12 +1603,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>färska och äldre ringhack på tall</t>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 7763-2026 artfynd.xlsx
+++ b/artfynd/A 7763-2026 artfynd.xlsx
@@ -1638,7 +1638,7 @@
         <v>131194261</v>
       </c>
       <c r="B10" t="n">
-        <v>79243</v>
+        <v>79244</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 7763-2026 artfynd.xlsx
+++ b/artfynd/A 7763-2026 artfynd.xlsx
@@ -1395,7 +1395,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131194264</v>
+        <v>131194260</v>
       </c>
       <c r="B8" t="n">
         <v>57884</v>
@@ -1438,10 +1438,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>599123</v>
+        <v>599106</v>
       </c>
       <c r="R8" t="n">
-        <v>6943474</v>
+        <v>6943538</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1473,7 +1473,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>färska och äldre ringhack på tall</t>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1515,7 +1515,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131194260</v>
+        <v>131194264</v>
       </c>
       <c r="B9" t="n">
         <v>57884</v>
@@ -1558,10 +1558,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>599106</v>
+        <v>599123</v>
       </c>
       <c r="R9" t="n">
-        <v>6943538</v>
+        <v>6943474</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1593,7 +1593,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1603,12 +1603,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>färska ringhack på tall</t>
+          <t>färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 7763-2026 artfynd.xlsx
+++ b/artfynd/A 7763-2026 artfynd.xlsx
@@ -1395,7 +1395,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131194260</v>
+        <v>131194264</v>
       </c>
       <c r="B8" t="n">
         <v>57884</v>
@@ -1438,10 +1438,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>599106</v>
+        <v>599123</v>
       </c>
       <c r="R8" t="n">
-        <v>6943538</v>
+        <v>6943474</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1473,7 +1473,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>färska ringhack på tall</t>
+          <t>färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1515,7 +1515,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131194264</v>
+        <v>131194260</v>
       </c>
       <c r="B9" t="n">
         <v>57884</v>
@@ -1558,10 +1558,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>599123</v>
+        <v>599106</v>
       </c>
       <c r="R9" t="n">
-        <v>6943474</v>
+        <v>6943538</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1593,7 +1593,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1603,12 +1603,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>färska och äldre ringhack på tall</t>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1638,7 +1638,7 @@
         <v>131194261</v>
       </c>
       <c r="B10" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 7763-2026 artfynd.xlsx
+++ b/artfynd/A 7763-2026 artfynd.xlsx
@@ -1638,7 +1638,7 @@
         <v>131194261</v>
       </c>
       <c r="B10" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 7763-2026 artfynd.xlsx
+++ b/artfynd/A 7763-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131194262</v>
       </c>
       <c r="B2" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>131194258</v>
       </c>
       <c r="B3" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>131194259</v>
       </c>
       <c r="B4" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
         <v>131194256</v>
       </c>
       <c r="B5" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1158,7 +1158,7 @@
         <v>131194257</v>
       </c>
       <c r="B6" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1278,7 +1278,7 @@
         <v>131194263</v>
       </c>
       <c r="B7" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1398,7 +1398,7 @@
         <v>131194264</v>
       </c>
       <c r="B8" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         <v>131194260</v>
       </c>
       <c r="B9" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         <v>131194261</v>
       </c>
       <c r="B10" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 7763-2026 artfynd.xlsx
+++ b/artfynd/A 7763-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131194262</v>
       </c>
       <c r="B2" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>131194258</v>
       </c>
       <c r="B3" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>131194259</v>
       </c>
       <c r="B4" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
         <v>131194256</v>
       </c>
       <c r="B5" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1158,7 +1158,7 @@
         <v>131194257</v>
       </c>
       <c r="B6" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1278,7 +1278,7 @@
         <v>131194263</v>
       </c>
       <c r="B7" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1398,7 +1398,7 @@
         <v>131194264</v>
       </c>
       <c r="B8" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         <v>131194260</v>
       </c>
       <c r="B9" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         <v>131194261</v>
       </c>
       <c r="B10" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 7763-2026 artfynd.xlsx
+++ b/artfynd/A 7763-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131194262</v>
       </c>
       <c r="B2" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>131194258</v>
       </c>
       <c r="B3" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>131194259</v>
       </c>
       <c r="B4" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
         <v>131194256</v>
       </c>
       <c r="B5" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1158,7 +1158,7 @@
         <v>131194257</v>
       </c>
       <c r="B6" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1278,7 +1278,7 @@
         <v>131194263</v>
       </c>
       <c r="B7" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1395,10 +1395,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131194264</v>
+        <v>131194260</v>
       </c>
       <c r="B8" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1438,10 +1438,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>599123</v>
+        <v>599106</v>
       </c>
       <c r="R8" t="n">
-        <v>6943474</v>
+        <v>6943538</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1473,7 +1473,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>färska och äldre ringhack på tall</t>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1515,10 +1515,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131194260</v>
+        <v>131194264</v>
       </c>
       <c r="B9" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1558,10 +1558,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>599106</v>
+        <v>599123</v>
       </c>
       <c r="R9" t="n">
-        <v>6943538</v>
+        <v>6943474</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1593,7 +1593,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1603,12 +1603,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>färska ringhack på tall</t>
+          <t>färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1638,7 +1638,7 @@
         <v>131194261</v>
       </c>
       <c r="B10" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 7763-2026 artfynd.xlsx
+++ b/artfynd/A 7763-2026 artfynd.xlsx
@@ -1395,7 +1395,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131194260</v>
+        <v>131194264</v>
       </c>
       <c r="B8" t="n">
         <v>57888</v>
@@ -1438,10 +1438,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>599106</v>
+        <v>599123</v>
       </c>
       <c r="R8" t="n">
-        <v>6943538</v>
+        <v>6943474</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1473,7 +1473,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>färska ringhack på tall</t>
+          <t>färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1515,7 +1515,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131194264</v>
+        <v>131194260</v>
       </c>
       <c r="B9" t="n">
         <v>57888</v>
@@ -1558,10 +1558,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>599123</v>
+        <v>599106</v>
       </c>
       <c r="R9" t="n">
-        <v>6943474</v>
+        <v>6943538</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1593,7 +1593,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1603,12 +1603,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>färska och äldre ringhack på tall</t>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 7763-2026 artfynd.xlsx
+++ b/artfynd/A 7763-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131194262</v>
       </c>
       <c r="B2" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>131194258</v>
       </c>
       <c r="B3" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>131194259</v>
       </c>
       <c r="B4" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
         <v>131194256</v>
       </c>
       <c r="B5" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1158,7 +1158,7 @@
         <v>131194257</v>
       </c>
       <c r="B6" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1278,7 +1278,7 @@
         <v>131194263</v>
       </c>
       <c r="B7" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1398,7 +1398,7 @@
         <v>131194264</v>
       </c>
       <c r="B8" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         <v>131194260</v>
       </c>
       <c r="B9" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         <v>131194261</v>
       </c>
       <c r="B10" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 7763-2026 artfynd.xlsx
+++ b/artfynd/A 7763-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131194262</v>
       </c>
       <c r="B2" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>131194258</v>
       </c>
       <c r="B3" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>131194259</v>
       </c>
       <c r="B4" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
         <v>131194256</v>
       </c>
       <c r="B5" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1158,7 +1158,7 @@
         <v>131194257</v>
       </c>
       <c r="B6" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1278,7 +1278,7 @@
         <v>131194263</v>
       </c>
       <c r="B7" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1398,7 +1398,7 @@
         <v>131194264</v>
       </c>
       <c r="B8" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         <v>131194260</v>
       </c>
       <c r="B9" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         <v>131194261</v>
       </c>
       <c r="B10" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 7763-2026 artfynd.xlsx
+++ b/artfynd/A 7763-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131194262</v>
+        <v>131194261</v>
       </c>
       <c r="B2" t="n">
-        <v>57898</v>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Starrmyran, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>599132</v>
+        <v>599136</v>
       </c>
       <c r="R2" t="n">
-        <v>6943496</v>
+        <v>6943509</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,12 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:47</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>färska ringhack på tall</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131194258</v>
+        <v>131194256</v>
       </c>
       <c r="B3" t="n">
-        <v>57898</v>
+        <v>57953</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -838,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>599054</v>
+        <v>599011</v>
       </c>
       <c r="R3" t="n">
-        <v>6943540</v>
+        <v>6943534</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -873,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -883,7 +870,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -915,10 +902,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131194259</v>
+        <v>131194257</v>
       </c>
       <c r="B4" t="n">
-        <v>57898</v>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -958,10 +945,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>599102</v>
+        <v>599017</v>
       </c>
       <c r="R4" t="n">
-        <v>6943551</v>
+        <v>6943536</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,7 +980,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1003,7 +990,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1035,10 +1022,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131194256</v>
+        <v>131194258</v>
       </c>
       <c r="B5" t="n">
-        <v>57898</v>
+        <v>57953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1078,10 +1065,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>599011</v>
+        <v>599054</v>
       </c>
       <c r="R5" t="n">
-        <v>6943534</v>
+        <v>6943540</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1113,7 +1100,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1123,7 +1110,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1155,10 +1142,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131194257</v>
+        <v>131194259</v>
       </c>
       <c r="B6" t="n">
-        <v>57898</v>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1198,10 +1185,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>599017</v>
+        <v>599102</v>
       </c>
       <c r="R6" t="n">
-        <v>6943536</v>
+        <v>6943551</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1233,7 +1220,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1243,7 +1230,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1275,10 +1262,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131194263</v>
+        <v>131194260</v>
       </c>
       <c r="B7" t="n">
-        <v>57898</v>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1318,10 +1305,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>599127</v>
+        <v>599106</v>
       </c>
       <c r="R7" t="n">
-        <v>6943474</v>
+        <v>6943538</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1353,7 +1340,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1363,7 +1350,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1395,10 +1382,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131194264</v>
+        <v>131194262</v>
       </c>
       <c r="B8" t="n">
-        <v>57898</v>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1438,10 +1425,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>599123</v>
+        <v>599132</v>
       </c>
       <c r="R8" t="n">
-        <v>6943474</v>
+        <v>6943496</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1473,7 +1460,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1483,12 +1470,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>färska och äldre ringhack på tall</t>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1515,10 +1502,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131194260</v>
+        <v>131194263</v>
       </c>
       <c r="B9" t="n">
-        <v>57898</v>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1558,10 +1545,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>599106</v>
+        <v>599127</v>
       </c>
       <c r="R9" t="n">
-        <v>6943538</v>
+        <v>6943474</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1593,7 +1580,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1603,7 +1590,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1635,10 +1622,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131194261</v>
+        <v>131194264</v>
       </c>
       <c r="B10" t="n">
-        <v>79260</v>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,34 +1633,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Starrmyran, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>599136</v>
+        <v>599123</v>
       </c>
       <c r="R10" t="n">
-        <v>6943509</v>
+        <v>6943474</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1705,7 +1700,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1715,7 +1710,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1739,6 +1739,126 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>131194265</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Starrmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>599093</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6943446</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Indal</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 7763-2026 artfynd.xlsx
+++ b/artfynd/A 7763-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131194261</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -899,6 +909,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131194256</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1019,6 +1034,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131194257</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1139,6 +1159,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131194258</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1259,6 +1284,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131194259</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1379,6 +1409,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131194260</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1499,6 +1534,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131194262</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1619,6 +1659,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131194263</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1739,6 +1784,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131194264</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1859,8 +1909,25 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131194265</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>